--- a/results/problem_two_stage_problem.xlsx
+++ b/results/problem_two_stage_problem.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C572"/>
+  <dimension ref="A1:C870"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>p_(0,_0,_0,_2)</t>
+          <t>p_(0,_0,_1,_0)</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>p_(0,_0,_1,_0)</t>
+          <t>p_(0,_1,_2,_3)</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -494,7 +494,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>p_(0,_0,_1,_2)</t>
+          <t>p_(0,_1,_2,_4)</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -507,7 +507,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>p_(0,_0,_2,_0)</t>
+          <t>p_(0,_1,_3,_2)</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>p_(0,_0,_2,_1)</t>
+          <t>p_(0,_1,_3,_4)</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -533,7 +533,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>p_(0,_1,_3,_4)</t>
+          <t>p_(0,_1,_4,_2)</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>p_(0,_2,_3,_4)</t>
+          <t>p_(0,_2,_2,_3)</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -572,7 +572,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>p_(0,_2,_4,_3)</t>
+          <t>p_(0,_2,_2,_4)</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -585,7 +585,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>p_(1,_0,_0,_1)</t>
+          <t>p_(0,_2,_3,_2)</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -598,7 +598,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>p_(1,_0,_0,_2)</t>
+          <t>p_(0,_2,_3,_4)</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -611,7 +611,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>p_(1,_0,_1,_0)</t>
+          <t>p_(0,_2,_4,_2)</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -624,7 +624,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>p_(1,_0,_1,_2)</t>
+          <t>p_(0,_2,_4,_3)</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -637,7 +637,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>p_(1,_0,_2,_0)</t>
+          <t>p_(1,_0,_0,_1)</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -650,7 +650,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>p_(1,_0,_2,_1)</t>
+          <t>p_(1,_0,_1,_0)</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>p_(1,_1,_3,_4)</t>
+          <t>p_(1,_1,_2,_3)</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -676,7 +676,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>p_(1,_1,_4,_3)</t>
+          <t>p_(1,_1,_2,_4)</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -689,7 +689,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>p_(1,_2,_3,_4)</t>
+          <t>p_(1,_1,_3,_2)</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -702,7 +702,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>p_(1,_2,_4,_3)</t>
+          <t>p_(1,_1,_3,_4)</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -715,11 +715,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>p_(2,_0,_0,_1)</t>
+          <t>p_(1,_1,_4,_2)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -728,11 +728,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>p_(2,_0,_0,_2)</t>
+          <t>p_(1,_1,_4,_3)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -741,11 +741,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>p_(2,_0,_1,_0)</t>
+          <t>p_(1,_2,_2,_3)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -754,11 +754,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>p_(2,_0,_1,_2)</t>
+          <t>p_(1,_2,_2,_4)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -767,11 +767,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>p_(2,_0,_2,_0)</t>
+          <t>p_(1,_2,_3,_2)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -780,11 +780,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>p_(2,_0,_2,_1)</t>
+          <t>p_(1,_2,_3,_4)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -793,7 +793,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>p_(2,_1,_3,_4)</t>
+          <t>p_(1,_2,_4,_2)</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>p_(2,_1,_4,_3)</t>
+          <t>p_(1,_2,_4,_3)</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>p_(2,_2,_3,_4)</t>
+          <t>p_(2,_0,_0,_1)</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>p_(2,_2,_4,_3)</t>
+          <t>p_(2,_0,_1,_0)</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -845,7 +845,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>q_(0,_0,_0,_1)</t>
+          <t>p_(2,_1,_2,_3)</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -858,7 +858,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>q_(0,_0,_0,_2)</t>
+          <t>p_(2,_1,_2,_4)</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>q_(0,_0,_1,_0)</t>
+          <t>p_(2,_1,_3,_2)</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -884,7 +884,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>q_(0,_0,_1,_2)</t>
+          <t>p_(2,_1,_3,_4)</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -897,7 +897,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>q_(0,_0,_2,_0)</t>
+          <t>p_(2,_1,_4,_2)</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>q_(0,_0,_2,_1)</t>
+          <t>p_(2,_1,_4,_3)</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>q_(0,_1,_3,_4)</t>
+          <t>p_(2,_2,_2,_3)</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -936,7 +936,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>q_(0,_1,_4,_3)</t>
+          <t>p_(2,_2,_2,_4)</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>q_(0,_2,_3,_4)</t>
+          <t>p_(2,_2,_3,_2)</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>q_(0,_2,_4,_3)</t>
+          <t>p_(2,_2,_3,_4)</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>q_(1,_0,_0,_1)</t>
+          <t>p_(2,_2,_4,_2)</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -988,7 +988,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>q_(1,_0,_0,_2)</t>
+          <t>p_(2,_2,_4,_3)</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1001,11 +1001,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>q_(1,_0,_1,_0)</t>
+          <t>p_(3,_0,_0,_1)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1014,11 +1014,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>q_(1,_0,_1,_2)</t>
+          <t>p_(3,_0,_1,_0)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>q_(1,_0,_2,_0)</t>
+          <t>p_(3,_1,_2,_3)</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>q_(1,_0,_2,_1)</t>
+          <t>p_(3,_1,_2,_4)</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>q_(1,_1,_3,_4)</t>
+          <t>p_(3,_1,_3,_2)</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>q_(1,_1,_4,_3)</t>
+          <t>p_(3,_1,_3,_4)</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>q_(1,_2,_3,_4)</t>
+          <t>p_(3,_1,_4,_2)</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>q_(1,_2,_4,_3)</t>
+          <t>p_(3,_1,_4,_3)</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1105,11 +1105,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>q_(2,_0,_0,_1)</t>
+          <t>p_(3,_2,_2,_3)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>q_(2,_0,_0,_2)</t>
+          <t>p_(3,_2,_2,_4)</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>q_(2,_0,_1,_0)</t>
+          <t>p_(3,_2,_3,_2)</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>q_(2,_0,_1,_2)</t>
+          <t>p_(3,_2,_3,_4)</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1157,11 +1157,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>q_(2,_0,_2,_0)</t>
+          <t>p_(3,_2,_4,_2)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1170,11 +1170,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>q_(2,_0,_2,_1)</t>
+          <t>p_(3,_2,_4,_3)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>q_(2,_1,_3,_4)</t>
+          <t>q_(0,_0,_0,_1)</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1196,11 +1196,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>q_(2,_1,_4,_3)</t>
+          <t>q_(0,_0,_1,_0)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>q_(2,_2,_3,_4)</t>
+          <t>q_(0,_1,_2,_3)</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1222,11 +1222,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>q_(2,_2,_4,_3)</t>
+          <t>q_(0,_1,_2,_4)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_00</t>
+          <t>q_(0,_1,_3,_2)</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_01</t>
+          <t>q_(0,_1,_3,_4)</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_02</t>
+          <t>q_(0,_1,_4,_2)</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_03</t>
+          <t>q_(0,_1,_4,_3)</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_04</t>
+          <t>q_(0,_2,_2,_3)</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_05</t>
+          <t>q_(0,_2,_2,_4)</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_06</t>
+          <t>q_(0,_2,_3,_2)</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_07</t>
+          <t>q_(0,_2,_3,_4)</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_08</t>
+          <t>q_(0,_2,_4,_2)</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_09</t>
+          <t>q_(0,_2,_4,_3)</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_10</t>
+          <t>q_(1,_0,_0,_1)</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_11</t>
+          <t>q_(1,_0,_1,_0)</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_12</t>
+          <t>q_(1,_1,_2,_3)</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_13</t>
+          <t>q_(1,_1,_2,_4)</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_14</t>
+          <t>q_(1,_1,_3,_2)</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_15</t>
+          <t>q_(1,_1,_3,_4)</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_16</t>
+          <t>q_(1,_1,_4,_2)</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_17</t>
+          <t>q_(1,_1,_4,_3)</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_18</t>
+          <t>q_(1,_2,_2,_3)</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_19</t>
+          <t>q_(1,_2,_2,_4)</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1495,11 +1495,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_20</t>
+          <t>q_(1,_2,_3,_2)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_21</t>
+          <t>q_(1,_2,_3,_4)</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_22</t>
+          <t>q_(1,_2,_4,_2)</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_0_23</t>
+          <t>q_(1,_2,_4,_3)</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_00</t>
+          <t>q_(2,_0,_0,_1)</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_01</t>
+          <t>q_(2,_0,_1,_0)</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_02</t>
+          <t>q_(2,_1,_2,_3)</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_03</t>
+          <t>q_(2,_1,_2,_4)</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_04</t>
+          <t>q_(2,_1,_3,_2)</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_05</t>
+          <t>q_(2,_1,_3,_4)</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_06</t>
+          <t>q_(2,_1,_4,_2)</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_07</t>
+          <t>q_(2,_1,_4,_3)</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_08</t>
+          <t>q_(2,_2,_2,_3)</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_09</t>
+          <t>q_(2,_2,_2,_4)</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_10</t>
+          <t>q_(2,_2,_3,_2)</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_11</t>
+          <t>q_(2,_2,_3,_4)</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_12</t>
+          <t>q_(2,_2,_4,_2)</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_13</t>
+          <t>q_(2,_2,_4,_3)</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -1729,11 +1729,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_14</t>
+          <t>q_(3,_0,_0,_1)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_15</t>
+          <t>q_(3,_0,_1,_0)</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_16</t>
+          <t>q_(3,_1,_2,_3)</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_17</t>
+          <t>q_(3,_1,_2,_4)</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_18</t>
+          <t>q_(3,_1,_3,_2)</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_19</t>
+          <t>q_(3,_1,_3,_4)</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_20</t>
+          <t>q_(3,_1,_4,_2)</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_21</t>
+          <t>q_(3,_1,_4,_3)</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_1_22</t>
+          <t>q_(3,_2,_2,_3)</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_00</t>
+          <t>q_(3,_2,_2,_4)</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_01</t>
+          <t>q_(3,_2,_3,_2)</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_02</t>
+          <t>q_(3,_2,_3,_4)</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_03</t>
+          <t>q_(3,_2,_4,_2)</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_04</t>
+          <t>q_(3,_2,_4,_3)</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_05</t>
+          <t>s_hour_scen0_0_0_00</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_06</t>
+          <t>s_hour_scen0_0_0_01</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_07</t>
+          <t>s_hour_scen0_0_0_02</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_08</t>
+          <t>s_hour_scen0_0_0_03</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_09</t>
+          <t>s_hour_scen0_0_0_04</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_10</t>
+          <t>s_hour_scen0_0_0_05</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_11</t>
+          <t>s_hour_scen0_0_0_06</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_12</t>
+          <t>s_hour_scen0_0_0_07</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_13</t>
+          <t>s_hour_scen0_0_0_08</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_14</t>
+          <t>s_hour_scen0_0_0_09</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_15</t>
+          <t>s_hour_scen0_0_0_10</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_16</t>
+          <t>s_hour_scen0_0_0_11</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_17</t>
+          <t>s_hour_scen0_0_0_12</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_18</t>
+          <t>s_hour_scen0_0_0_13</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_19</t>
+          <t>s_hour_scen0_0_0_14</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>s_hour_scen0_0_2_20</t>
+          <t>s_hour_scen0_0_0_15</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_00</t>
+          <t>s_hour_scen0_0_0_16</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_01</t>
+          <t>s_hour_scen0_0_0_17</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_02</t>
+          <t>s_hour_scen0_0_0_18</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_03</t>
+          <t>s_hour_scen0_0_0_19</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_04</t>
+          <t>s_hour_scen0_0_0_20</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_05</t>
+          <t>s_hour_scen0_0_0_21</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_06</t>
+          <t>s_hour_scen0_0_0_22</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_07</t>
+          <t>s_hour_scen0_0_1_00</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_08</t>
+          <t>s_hour_scen0_0_1_01</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_09</t>
+          <t>s_hour_scen0_0_1_02</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_10</t>
+          <t>s_hour_scen0_0_1_03</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_11</t>
+          <t>s_hour_scen0_0_1_04</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_12</t>
+          <t>s_hour_scen0_0_1_05</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_13</t>
+          <t>s_hour_scen0_0_1_06</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_14</t>
+          <t>s_hour_scen0_0_1_07</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_15</t>
+          <t>s_hour_scen0_0_1_08</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_16</t>
+          <t>s_hour_scen0_0_1_09</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_17</t>
+          <t>s_hour_scen0_0_1_10</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_18</t>
+          <t>s_hour_scen0_0_1_11</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_19</t>
+          <t>s_hour_scen0_0_1_12</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_20</t>
+          <t>s_hour_scen0_0_1_13</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_3_21</t>
+          <t>s_hour_scen0_0_1_14</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_00</t>
+          <t>s_hour_scen0_0_1_15</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_01</t>
+          <t>s_hour_scen0_0_1_16</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_02</t>
+          <t>s_hour_scen0_0_1_17</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_03</t>
+          <t>s_hour_scen0_0_1_18</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_04</t>
+          <t>s_hour_scen0_0_1_19</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_05</t>
+          <t>s_hour_scen0_0_1_20</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_06</t>
+          <t>s_hour_scen0_1_2_00</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_07</t>
+          <t>s_hour_scen0_1_2_01</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_08</t>
+          <t>s_hour_scen0_1_2_02</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_09</t>
+          <t>s_hour_scen0_1_2_03</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_10</t>
+          <t>s_hour_scen0_1_2_04</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_11</t>
+          <t>s_hour_scen0_1_2_05</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_12</t>
+          <t>s_hour_scen0_1_2_06</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_13</t>
+          <t>s_hour_scen0_1_2_07</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_14</t>
+          <t>s_hour_scen0_1_2_08</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_15</t>
+          <t>s_hour_scen0_1_2_09</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_16</t>
+          <t>s_hour_scen0_1_2_10</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_17</t>
+          <t>s_hour_scen0_1_2_11</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_18</t>
+          <t>s_hour_scen0_1_2_12</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_19</t>
+          <t>s_hour_scen0_1_2_13</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_20</t>
+          <t>s_hour_scen0_1_2_14</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_21</t>
+          <t>s_hour_scen0_1_2_15</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>s_hour_scen0_1_4_22</t>
+          <t>s_hour_scen0_1_2_16</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_00</t>
+          <t>s_hour_scen0_1_2_17</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_01</t>
+          <t>s_hour_scen0_1_2_18</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_02</t>
+          <t>s_hour_scen0_1_2_19</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_03</t>
+          <t>s_hour_scen0_1_3_00</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_04</t>
+          <t>s_hour_scen0_1_3_01</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_05</t>
+          <t>s_hour_scen0_1_3_02</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_06</t>
+          <t>s_hour_scen0_1_3_03</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_07</t>
+          <t>s_hour_scen0_1_3_04</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_08</t>
+          <t>s_hour_scen0_1_3_05</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_09</t>
+          <t>s_hour_scen0_1_3_06</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_10</t>
+          <t>s_hour_scen0_1_3_07</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_11</t>
+          <t>s_hour_scen0_1_3_08</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_12</t>
+          <t>s_hour_scen0_1_3_09</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_13</t>
+          <t>s_hour_scen0_1_3_10</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_14</t>
+          <t>s_hour_scen0_1_3_11</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_15</t>
+          <t>s_hour_scen0_1_3_12</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_16</t>
+          <t>s_hour_scen0_1_3_13</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_17</t>
+          <t>s_hour_scen0_1_3_14</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_18</t>
+          <t>s_hour_scen0_1_3_15</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_19</t>
+          <t>s_hour_scen0_1_3_16</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_20</t>
+          <t>s_hour_scen0_1_3_17</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_3_21</t>
+          <t>s_hour_scen0_1_3_18</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_00</t>
+          <t>s_hour_scen0_1_3_19</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_01</t>
+          <t>s_hour_scen0_1_3_20</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_02</t>
+          <t>s_hour_scen0_1_3_21</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_03</t>
+          <t>s_hour_scen0_1_4_00</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_04</t>
+          <t>s_hour_scen0_1_4_01</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_05</t>
+          <t>s_hour_scen0_1_4_02</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_06</t>
+          <t>s_hour_scen0_1_4_03</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_07</t>
+          <t>s_hour_scen0_1_4_04</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_08</t>
+          <t>s_hour_scen0_1_4_05</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_09</t>
+          <t>s_hour_scen0_1_4_06</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_10</t>
+          <t>s_hour_scen0_1_4_07</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_11</t>
+          <t>s_hour_scen0_1_4_08</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_12</t>
+          <t>s_hour_scen0_1_4_09</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_13</t>
+          <t>s_hour_scen0_1_4_10</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_14</t>
+          <t>s_hour_scen0_1_4_11</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_15</t>
+          <t>s_hour_scen0_1_4_12</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_16</t>
+          <t>s_hour_scen0_1_4_13</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_17</t>
+          <t>s_hour_scen0_1_4_14</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_18</t>
+          <t>s_hour_scen0_1_4_15</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_19</t>
+          <t>s_hour_scen0_1_4_16</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_20</t>
+          <t>s_hour_scen0_1_4_17</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_21</t>
+          <t>s_hour_scen0_1_4_18</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>s_hour_scen0_2_4_22</t>
+          <t>s_hour_scen0_1_4_19</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_00</t>
+          <t>s_hour_scen0_1_4_20</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_01</t>
+          <t>s_hour_scen0_1_4_21</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_02</t>
+          <t>s_hour_scen0_1_4_22</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_03</t>
+          <t>s_hour_scen0_1_4_23</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_04</t>
+          <t>s_hour_scen0_2_2_00</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_05</t>
+          <t>s_hour_scen0_2_2_01</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_06</t>
+          <t>s_hour_scen0_2_2_02</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_07</t>
+          <t>s_hour_scen0_2_2_03</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_08</t>
+          <t>s_hour_scen0_2_2_04</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_09</t>
+          <t>s_hour_scen0_2_2_05</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_10</t>
+          <t>s_hour_scen0_2_2_06</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_11</t>
+          <t>s_hour_scen0_2_2_07</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_12</t>
+          <t>s_hour_scen0_2_2_08</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_13</t>
+          <t>s_hour_scen0_2_2_09</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_14</t>
+          <t>s_hour_scen0_2_2_10</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_15</t>
+          <t>s_hour_scen0_2_2_11</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_16</t>
+          <t>s_hour_scen0_2_2_12</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_17</t>
+          <t>s_hour_scen0_2_2_13</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_18</t>
+          <t>s_hour_scen0_2_2_14</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_19</t>
+          <t>s_hour_scen0_2_2_15</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -3549,11 +3549,11 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_20</t>
+          <t>s_hour_scen0_2_2_16</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_21</t>
+          <t>s_hour_scen0_2_2_17</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_22</t>
+          <t>s_hour_scen0_2_2_18</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_0_23</t>
+          <t>s_hour_scen0_2_2_19</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_00</t>
+          <t>s_hour_scen0_2_3_00</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_01</t>
+          <t>s_hour_scen0_2_3_01</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_02</t>
+          <t>s_hour_scen0_2_3_02</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_03</t>
+          <t>s_hour_scen0_2_3_03</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_04</t>
+          <t>s_hour_scen0_2_3_04</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_05</t>
+          <t>s_hour_scen0_2_3_05</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_06</t>
+          <t>s_hour_scen0_2_3_06</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_07</t>
+          <t>s_hour_scen0_2_3_07</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_08</t>
+          <t>s_hour_scen0_2_3_08</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_09</t>
+          <t>s_hour_scen0_2_3_09</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_10</t>
+          <t>s_hour_scen0_2_3_10</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_11</t>
+          <t>s_hour_scen0_2_3_11</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_12</t>
+          <t>s_hour_scen0_2_3_12</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_13</t>
+          <t>s_hour_scen0_2_3_13</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_14</t>
+          <t>s_hour_scen0_2_3_14</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_15</t>
+          <t>s_hour_scen0_2_3_15</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_16</t>
+          <t>s_hour_scen0_2_3_16</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_17</t>
+          <t>s_hour_scen0_2_3_17</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_18</t>
+          <t>s_hour_scen0_2_3_18</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_19</t>
+          <t>s_hour_scen0_2_3_19</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_20</t>
+          <t>s_hour_scen0_2_3_20</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_21</t>
+          <t>s_hour_scen0_2_3_21</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_1_22</t>
+          <t>s_hour_scen0_2_4_00</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_00</t>
+          <t>s_hour_scen0_2_4_01</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_01</t>
+          <t>s_hour_scen0_2_4_02</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_02</t>
+          <t>s_hour_scen0_2_4_03</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_03</t>
+          <t>s_hour_scen0_2_4_04</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_04</t>
+          <t>s_hour_scen0_2_4_05</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_05</t>
+          <t>s_hour_scen0_2_4_06</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_06</t>
+          <t>s_hour_scen0_2_4_07</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_07</t>
+          <t>s_hour_scen0_2_4_08</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_08</t>
+          <t>s_hour_scen0_2_4_09</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_09</t>
+          <t>s_hour_scen0_2_4_10</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_10</t>
+          <t>s_hour_scen0_2_4_11</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_11</t>
+          <t>s_hour_scen0_2_4_12</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_12</t>
+          <t>s_hour_scen0_2_4_13</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_13</t>
+          <t>s_hour_scen0_2_4_14</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_14</t>
+          <t>s_hour_scen0_2_4_15</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_15</t>
+          <t>s_hour_scen0_2_4_16</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_16</t>
+          <t>s_hour_scen0_2_4_17</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_17</t>
+          <t>s_hour_scen0_2_4_18</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_18</t>
+          <t>s_hour_scen0_2_4_19</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_19</t>
+          <t>s_hour_scen0_2_4_20</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>s_hour_scen1_0_2_20</t>
+          <t>s_hour_scen0_2_4_21</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_00</t>
+          <t>s_hour_scen0_2_4_22</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_01</t>
+          <t>s_hour_scen0_2_4_23</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_02</t>
+          <t>s_hour_scen1_0_0_00</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_03</t>
+          <t>s_hour_scen1_0_0_01</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_04</t>
+          <t>s_hour_scen1_0_0_02</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_05</t>
+          <t>s_hour_scen1_0_0_03</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_06</t>
+          <t>s_hour_scen1_0_0_04</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_07</t>
+          <t>s_hour_scen1_0_0_05</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_08</t>
+          <t>s_hour_scen1_0_0_06</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_09</t>
+          <t>s_hour_scen1_0_0_07</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_10</t>
+          <t>s_hour_scen1_0_0_08</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_11</t>
+          <t>s_hour_scen1_0_0_09</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_12</t>
+          <t>s_hour_scen1_0_0_10</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_13</t>
+          <t>s_hour_scen1_0_0_11</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_14</t>
+          <t>s_hour_scen1_0_0_12</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_15</t>
+          <t>s_hour_scen1_0_0_13</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_16</t>
+          <t>s_hour_scen1_0_0_14</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_17</t>
+          <t>s_hour_scen1_0_0_15</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_18</t>
+          <t>s_hour_scen1_0_0_16</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_19</t>
+          <t>s_hour_scen1_0_0_17</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_20</t>
+          <t>s_hour_scen1_0_0_18</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_3_21</t>
+          <t>s_hour_scen1_0_0_19</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_00</t>
+          <t>s_hour_scen1_0_0_20</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_01</t>
+          <t>s_hour_scen1_0_0_21</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_02</t>
+          <t>s_hour_scen1_0_0_22</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_03</t>
+          <t>s_hour_scen1_0_1_00</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_04</t>
+          <t>s_hour_scen1_0_1_01</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_05</t>
+          <t>s_hour_scen1_0_1_02</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_06</t>
+          <t>s_hour_scen1_0_1_03</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_07</t>
+          <t>s_hour_scen1_0_1_04</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_08</t>
+          <t>s_hour_scen1_0_1_05</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_09</t>
+          <t>s_hour_scen1_0_1_06</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_10</t>
+          <t>s_hour_scen1_0_1_07</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_11</t>
+          <t>s_hour_scen1_0_1_08</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_12</t>
+          <t>s_hour_scen1_0_1_09</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_13</t>
+          <t>s_hour_scen1_0_1_10</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_14</t>
+          <t>s_hour_scen1_0_1_11</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_15</t>
+          <t>s_hour_scen1_0_1_12</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_16</t>
+          <t>s_hour_scen1_0_1_13</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_17</t>
+          <t>s_hour_scen1_0_1_14</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_18</t>
+          <t>s_hour_scen1_0_1_15</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_19</t>
+          <t>s_hour_scen1_0_1_16</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_20</t>
+          <t>s_hour_scen1_0_1_17</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_21</t>
+          <t>s_hour_scen1_0_1_18</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>s_hour_scen1_1_4_22</t>
+          <t>s_hour_scen1_0_1_19</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_00</t>
+          <t>s_hour_scen1_0_1_20</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_01</t>
+          <t>s_hour_scen1_1_2_00</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_02</t>
+          <t>s_hour_scen1_1_2_01</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_03</t>
+          <t>s_hour_scen1_1_2_02</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_04</t>
+          <t>s_hour_scen1_1_2_03</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_05</t>
+          <t>s_hour_scen1_1_2_04</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_06</t>
+          <t>s_hour_scen1_1_2_05</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_07</t>
+          <t>s_hour_scen1_1_2_06</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_08</t>
+          <t>s_hour_scen1_1_2_07</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_09</t>
+          <t>s_hour_scen1_1_2_08</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_10</t>
+          <t>s_hour_scen1_1_2_09</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_11</t>
+          <t>s_hour_scen1_1_2_10</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_12</t>
+          <t>s_hour_scen1_1_2_11</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_13</t>
+          <t>s_hour_scen1_1_2_12</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_14</t>
+          <t>s_hour_scen1_1_2_13</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_15</t>
+          <t>s_hour_scen1_1_2_14</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_16</t>
+          <t>s_hour_scen1_1_2_15</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_17</t>
+          <t>s_hour_scen1_1_2_16</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_18</t>
+          <t>s_hour_scen1_1_2_17</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_19</t>
+          <t>s_hour_scen1_1_2_18</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_20</t>
+          <t>s_hour_scen1_1_2_19</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_3_21</t>
+          <t>s_hour_scen1_1_3_00</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_00</t>
+          <t>s_hour_scen1_1_3_01</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_01</t>
+          <t>s_hour_scen1_1_3_02</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_02</t>
+          <t>s_hour_scen1_1_3_03</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_03</t>
+          <t>s_hour_scen1_1_3_04</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_04</t>
+          <t>s_hour_scen1_1_3_05</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_05</t>
+          <t>s_hour_scen1_1_3_06</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_06</t>
+          <t>s_hour_scen1_1_3_07</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_07</t>
+          <t>s_hour_scen1_1_3_08</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_08</t>
+          <t>s_hour_scen1_1_3_09</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_09</t>
+          <t>s_hour_scen1_1_3_10</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_10</t>
+          <t>s_hour_scen1_1_3_11</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_11</t>
+          <t>s_hour_scen1_1_3_12</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_12</t>
+          <t>s_hour_scen1_1_3_13</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_13</t>
+          <t>s_hour_scen1_1_3_14</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_14</t>
+          <t>s_hour_scen1_1_3_15</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_15</t>
+          <t>s_hour_scen1_1_3_16</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_16</t>
+          <t>s_hour_scen1_1_3_17</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_17</t>
+          <t>s_hour_scen1_1_3_18</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_18</t>
+          <t>s_hour_scen1_1_3_19</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_19</t>
+          <t>s_hour_scen1_1_3_20</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_20</t>
+          <t>s_hour_scen1_1_3_21</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_21</t>
+          <t>s_hour_scen1_1_4_00</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>s_hour_scen1_2_4_22</t>
+          <t>s_hour_scen1_1_4_01</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_00</t>
+          <t>s_hour_scen1_1_4_02</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_01</t>
+          <t>s_hour_scen1_1_4_03</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_02</t>
+          <t>s_hour_scen1_1_4_04</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_03</t>
+          <t>s_hour_scen1_1_4_05</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_04</t>
+          <t>s_hour_scen1_1_4_06</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_05</t>
+          <t>s_hour_scen1_1_4_07</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_06</t>
+          <t>s_hour_scen1_1_4_08</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_07</t>
+          <t>s_hour_scen1_1_4_09</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_08</t>
+          <t>s_hour_scen1_1_4_10</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_09</t>
+          <t>s_hour_scen1_1_4_11</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -5473,11 +5473,11 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_10</t>
+          <t>s_hour_scen1_1_4_12</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_11</t>
+          <t>s_hour_scen1_1_4_13</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_12</t>
+          <t>s_hour_scen1_1_4_14</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_13</t>
+          <t>s_hour_scen1_1_4_15</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_14</t>
+          <t>s_hour_scen1_1_4_16</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_15</t>
+          <t>s_hour_scen1_1_4_17</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_16</t>
+          <t>s_hour_scen1_1_4_18</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_17</t>
+          <t>s_hour_scen1_1_4_19</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_18</t>
+          <t>s_hour_scen1_1_4_20</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_19</t>
+          <t>s_hour_scen1_1_4_21</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_20</t>
+          <t>s_hour_scen1_1_4_22</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_21</t>
+          <t>s_hour_scen1_1_4_23</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_22</t>
+          <t>s_hour_scen1_2_2_00</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_0_23</t>
+          <t>s_hour_scen1_2_2_01</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_00</t>
+          <t>s_hour_scen1_2_2_02</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_01</t>
+          <t>s_hour_scen1_2_2_03</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_02</t>
+          <t>s_hour_scen1_2_2_04</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_03</t>
+          <t>s_hour_scen1_2_2_05</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_04</t>
+          <t>s_hour_scen1_2_2_06</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_05</t>
+          <t>s_hour_scen1_2_2_07</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_06</t>
+          <t>s_hour_scen1_2_2_08</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_07</t>
+          <t>s_hour_scen1_2_2_09</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_08</t>
+          <t>s_hour_scen1_2_2_10</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_09</t>
+          <t>s_hour_scen1_2_2_11</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_10</t>
+          <t>s_hour_scen1_2_2_12</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_11</t>
+          <t>s_hour_scen1_2_2_13</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_12</t>
+          <t>s_hour_scen1_2_2_14</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_13</t>
+          <t>s_hour_scen1_2_2_15</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_14</t>
+          <t>s_hour_scen1_2_2_16</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_15</t>
+          <t>s_hour_scen1_2_2_17</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -5863,11 +5863,11 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_16</t>
+          <t>s_hour_scen1_2_2_18</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_17</t>
+          <t>s_hour_scen1_2_2_19</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_18</t>
+          <t>s_hour_scen1_2_3_00</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_19</t>
+          <t>s_hour_scen1_2_3_01</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_20</t>
+          <t>s_hour_scen1_2_3_02</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_21</t>
+          <t>s_hour_scen1_2_3_03</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_1_22</t>
+          <t>s_hour_scen1_2_3_04</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_00</t>
+          <t>s_hour_scen1_2_3_05</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -5967,11 +5967,11 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_01</t>
+          <t>s_hour_scen1_2_3_06</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="428">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_02</t>
+          <t>s_hour_scen1_2_3_07</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_03</t>
+          <t>s_hour_scen1_2_3_08</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_04</t>
+          <t>s_hour_scen1_2_3_09</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_05</t>
+          <t>s_hour_scen1_2_3_10</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_06</t>
+          <t>s_hour_scen1_2_3_11</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_07</t>
+          <t>s_hour_scen1_2_3_12</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_08</t>
+          <t>s_hour_scen1_2_3_13</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_09</t>
+          <t>s_hour_scen1_2_3_14</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_10</t>
+          <t>s_hour_scen1_2_3_15</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_11</t>
+          <t>s_hour_scen1_2_3_16</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_12</t>
+          <t>s_hour_scen1_2_3_17</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_13</t>
+          <t>s_hour_scen1_2_3_18</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_14</t>
+          <t>s_hour_scen1_2_3_19</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_15</t>
+          <t>s_hour_scen1_2_3_20</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_16</t>
+          <t>s_hour_scen1_2_3_21</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_17</t>
+          <t>s_hour_scen1_2_4_00</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_18</t>
+          <t>s_hour_scen1_2_4_01</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_19</t>
+          <t>s_hour_scen1_2_4_02</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>s_hour_scen2_0_2_20</t>
+          <t>s_hour_scen1_2_4_03</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_00</t>
+          <t>s_hour_scen1_2_4_04</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_01</t>
+          <t>s_hour_scen1_2_4_05</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_02</t>
+          <t>s_hour_scen1_2_4_06</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_03</t>
+          <t>s_hour_scen1_2_4_07</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_04</t>
+          <t>s_hour_scen1_2_4_08</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_05</t>
+          <t>s_hour_scen1_2_4_09</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_06</t>
+          <t>s_hour_scen1_2_4_10</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_07</t>
+          <t>s_hour_scen1_2_4_11</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_08</t>
+          <t>s_hour_scen1_2_4_12</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_09</t>
+          <t>s_hour_scen1_2_4_13</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_10</t>
+          <t>s_hour_scen1_2_4_14</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_11</t>
+          <t>s_hour_scen1_2_4_15</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_12</t>
+          <t>s_hour_scen1_2_4_16</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_13</t>
+          <t>s_hour_scen1_2_4_17</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_14</t>
+          <t>s_hour_scen1_2_4_18</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -6422,11 +6422,11 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_15</t>
+          <t>s_hour_scen1_2_4_19</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="463">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_16</t>
+          <t>s_hour_scen1_2_4_20</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_17</t>
+          <t>s_hour_scen1_2_4_21</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_18</t>
+          <t>s_hour_scen1_2_4_22</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_19</t>
+          <t>s_hour_scen1_2_4_23</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_20</t>
+          <t>s_hour_scen2_0_0_00</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_3_21</t>
+          <t>s_hour_scen2_0_0_01</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_00</t>
+          <t>s_hour_scen2_0_0_02</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_01</t>
+          <t>s_hour_scen2_0_0_03</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_02</t>
+          <t>s_hour_scen2_0_0_04</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_03</t>
+          <t>s_hour_scen2_0_0_05</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_04</t>
+          <t>s_hour_scen2_0_0_06</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_05</t>
+          <t>s_hour_scen2_0_0_07</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_06</t>
+          <t>s_hour_scen2_0_0_08</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_07</t>
+          <t>s_hour_scen2_0_0_09</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_08</t>
+          <t>s_hour_scen2_0_0_10</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_09</t>
+          <t>s_hour_scen2_0_0_11</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_10</t>
+          <t>s_hour_scen2_0_0_12</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_11</t>
+          <t>s_hour_scen2_0_0_13</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_12</t>
+          <t>s_hour_scen2_0_0_14</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_13</t>
+          <t>s_hour_scen2_0_0_15</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_14</t>
+          <t>s_hour_scen2_0_0_16</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_15</t>
+          <t>s_hour_scen2_0_0_17</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_16</t>
+          <t>s_hour_scen2_0_0_18</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_17</t>
+          <t>s_hour_scen2_0_0_19</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_18</t>
+          <t>s_hour_scen2_0_0_20</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_19</t>
+          <t>s_hour_scen2_0_0_21</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_20</t>
+          <t>s_hour_scen2_0_0_22</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_21</t>
+          <t>s_hour_scen2_0_1_00</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>s_hour_scen2_1_4_22</t>
+          <t>s_hour_scen2_0_1_01</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_00</t>
+          <t>s_hour_scen2_0_1_02</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_01</t>
+          <t>s_hour_scen2_0_1_03</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_02</t>
+          <t>s_hour_scen2_0_1_04</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_03</t>
+          <t>s_hour_scen2_0_1_05</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_04</t>
+          <t>s_hour_scen2_0_1_06</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_05</t>
+          <t>s_hour_scen2_0_1_07</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_06</t>
+          <t>s_hour_scen2_0_1_08</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_07</t>
+          <t>s_hour_scen2_0_1_09</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_08</t>
+          <t>s_hour_scen2_0_1_10</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_09</t>
+          <t>s_hour_scen2_0_1_11</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_10</t>
+          <t>s_hour_scen2_0_1_12</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_11</t>
+          <t>s_hour_scen2_0_1_13</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_12</t>
+          <t>s_hour_scen2_0_1_14</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_13</t>
+          <t>s_hour_scen2_0_1_15</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_14</t>
+          <t>s_hour_scen2_0_1_16</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_15</t>
+          <t>s_hour_scen2_0_1_17</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_16</t>
+          <t>s_hour_scen2_0_1_18</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_17</t>
+          <t>s_hour_scen2_0_1_19</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_18</t>
+          <t>s_hour_scen2_0_1_20</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_19</t>
+          <t>s_hour_scen2_1_2_00</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_20</t>
+          <t>s_hour_scen2_1_2_01</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_3_21</t>
+          <t>s_hour_scen2_1_2_02</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_00</t>
+          <t>s_hour_scen2_1_2_03</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_01</t>
+          <t>s_hour_scen2_1_2_04</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_02</t>
+          <t>s_hour_scen2_1_2_05</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_03</t>
+          <t>s_hour_scen2_1_2_06</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_04</t>
+          <t>s_hour_scen2_1_2_07</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_05</t>
+          <t>s_hour_scen2_1_2_08</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_06</t>
+          <t>s_hour_scen2_1_2_09</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_07</t>
+          <t>s_hour_scen2_1_2_10</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_08</t>
+          <t>s_hour_scen2_1_2_11</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_09</t>
+          <t>s_hour_scen2_1_2_12</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_10</t>
+          <t>s_hour_scen2_1_2_13</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_11</t>
+          <t>s_hour_scen2_1_2_14</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_12</t>
+          <t>s_hour_scen2_1_2_15</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_13</t>
+          <t>s_hour_scen2_1_2_16</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_14</t>
+          <t>s_hour_scen2_1_2_17</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_15</t>
+          <t>s_hour_scen2_1_2_18</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -7306,11 +7306,11 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_16</t>
+          <t>s_hour_scen2_1_2_19</t>
         </is>
       </c>
       <c r="C530" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="531">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_17</t>
+          <t>s_hour_scen2_1_3_00</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_18</t>
+          <t>s_hour_scen2_1_3_01</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_19</t>
+          <t>s_hour_scen2_1_3_02</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_20</t>
+          <t>s_hour_scen2_1_3_03</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_21</t>
+          <t>s_hour_scen2_1_3_04</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>s_hour_scen2_2_4_22</t>
+          <t>s_hour_scen2_1_3_05</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -7397,11 +7397,11 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>startingtime_(0,_0)</t>
+          <t>s_hour_scen2_1_3_06</t>
         </is>
       </c>
       <c r="C537" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="538">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>startingtime_(0,_1)</t>
+          <t>s_hour_scen2_1_3_07</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>startingtime_(0,_2)</t>
+          <t>s_hour_scen2_1_3_08</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>startingtime_(0,_3)</t>
+          <t>s_hour_scen2_1_3_09</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>startingtime_(0,_4)</t>
+          <t>s_hour_scen2_1_3_10</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -7462,11 +7462,11 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>startingtime_(1,_0)</t>
+          <t>s_hour_scen2_1_3_11</t>
         </is>
       </c>
       <c r="C542" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="543">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>startingtime_(1,_1)</t>
+          <t>s_hour_scen2_1_3_12</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>startingtime_(1,_2)</t>
+          <t>s_hour_scen2_1_3_13</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>startingtime_(1,_3)</t>
+          <t>s_hour_scen2_1_3_14</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>startingtime_(1,_4)</t>
+          <t>s_hour_scen2_1_3_15</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -7527,11 +7527,11 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>startingtime_(2,_0)</t>
+          <t>s_hour_scen2_1_3_16</t>
         </is>
       </c>
       <c r="C547" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="548">
@@ -7540,11 +7540,11 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>startingtime_(2,_1)</t>
+          <t>s_hour_scen2_1_3_17</t>
         </is>
       </c>
       <c r="C548" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="549">
@@ -7553,11 +7553,11 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>startingtime_(2,_2)</t>
+          <t>s_hour_scen2_1_3_18</t>
         </is>
       </c>
       <c r="C549" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="550">
@@ -7566,11 +7566,11 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>startingtime_(2,_3)</t>
+          <t>s_hour_scen2_1_3_19</t>
         </is>
       </c>
       <c r="C550" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="551">
@@ -7579,11 +7579,11 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>startingtime_(2,_4)</t>
+          <t>s_hour_scen2_1_3_20</t>
         </is>
       </c>
       <c r="C551" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="552">
@@ -7592,11 +7592,11 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>x_(0,_0,_0)</t>
+          <t>s_hour_scen2_1_3_21</t>
         </is>
       </c>
       <c r="C552" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="553">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>x_(0,_0,_1)</t>
+          <t>s_hour_scen2_1_4_00</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>x_(0,_0,_2)</t>
+          <t>s_hour_scen2_1_4_01</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>x_(0,_1,_3)</t>
+          <t>s_hour_scen2_1_4_02</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>x_(0,_1,_4)</t>
+          <t>s_hour_scen2_1_4_03</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>x_(0,_2,_3)</t>
+          <t>s_hour_scen2_1_4_04</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>x_(0,_2,_4)</t>
+          <t>s_hour_scen2_1_4_05</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -7683,11 +7683,11 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>x_(1,_0,_0)</t>
+          <t>s_hour_scen2_1_4_06</t>
         </is>
       </c>
       <c r="C559" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="560">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>x_(1,_0,_1)</t>
+          <t>s_hour_scen2_1_4_07</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>x_(1,_0,_2)</t>
+          <t>s_hour_scen2_1_4_08</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>x_(1,_1,_3)</t>
+          <t>s_hour_scen2_1_4_09</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>x_(1,_1,_4)</t>
+          <t>s_hour_scen2_1_4_10</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>x_(1,_2,_3)</t>
+          <t>s_hour_scen2_1_4_11</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>x_(1,_2,_4)</t>
+          <t>s_hour_scen2_1_4_12</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -7774,11 +7774,11 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>x_(2,_0,_0)</t>
+          <t>s_hour_scen2_1_4_13</t>
         </is>
       </c>
       <c r="C566" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="567">
@@ -7787,11 +7787,11 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>x_(2,_0,_1)</t>
+          <t>s_hour_scen2_1_4_14</t>
         </is>
       </c>
       <c r="C567" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="568">
@@ -7800,11 +7800,11 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>x_(2,_0,_2)</t>
+          <t>s_hour_scen2_1_4_15</t>
         </is>
       </c>
       <c r="C568" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="569">
@@ -7813,11 +7813,11 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>x_(2,_1,_3)</t>
+          <t>s_hour_scen2_1_4_16</t>
         </is>
       </c>
       <c r="C569" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="570">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>x_(2,_1,_4)</t>
+          <t>s_hour_scen2_1_4_17</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>x_(2,_2,_3)</t>
+          <t>s_hour_scen2_1_4_18</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -7852,11 +7852,3885 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
+          <t>s_hour_scen2_1_4_19</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="n">
+        <v>571</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_1_4_20</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="n">
+        <v>572</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_1_4_21</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="n">
+        <v>573</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_1_4_22</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="n">
+        <v>574</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_1_4_23</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="n">
+        <v>575</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_00</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="n">
+        <v>576</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_01</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="n">
+        <v>577</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_02</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="n">
+        <v>578</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_03</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="n">
+        <v>579</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_04</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="n">
+        <v>580</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_05</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="n">
+        <v>581</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_06</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="n">
+        <v>582</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_07</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="n">
+        <v>583</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_08</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="n">
+        <v>584</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_09</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="n">
+        <v>585</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_10</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="n">
+        <v>586</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_11</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="n">
+        <v>587</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_12</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="n">
+        <v>588</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_13</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="n">
+        <v>589</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_14</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="n">
+        <v>590</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_15</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="n">
+        <v>591</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_16</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="n">
+        <v>592</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_17</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="n">
+        <v>593</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_18</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="n">
+        <v>594</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_2_19</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="n">
+        <v>595</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_00</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="n">
+        <v>596</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_01</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="n">
+        <v>597</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_02</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="n">
+        <v>598</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_03</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="n">
+        <v>599</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_04</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="n">
+        <v>600</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_05</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="n">
+        <v>601</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_06</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="n">
+        <v>602</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_07</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="n">
+        <v>603</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_08</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="n">
+        <v>604</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_09</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="n">
+        <v>605</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_10</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="n">
+        <v>606</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_11</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="n">
+        <v>607</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_12</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="n">
+        <v>608</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_13</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="n">
+        <v>609</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_14</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="n">
+        <v>610</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_15</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="n">
+        <v>611</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_16</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="n">
+        <v>612</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_17</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="n">
+        <v>613</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_18</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="n">
+        <v>614</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_19</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="n">
+        <v>615</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_20</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="n">
+        <v>616</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_3_21</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="n">
+        <v>617</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_00</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="n">
+        <v>618</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_01</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="n">
+        <v>619</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_02</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="n">
+        <v>620</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_03</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="n">
+        <v>621</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_04</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="n">
+        <v>622</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_05</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="n">
+        <v>623</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_06</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="n">
+        <v>624</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_07</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="n">
+        <v>625</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_08</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="n">
+        <v>626</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_09</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="n">
+        <v>627</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_10</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="n">
+        <v>628</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_11</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="n">
+        <v>629</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_12</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="n">
+        <v>630</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_13</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="n">
+        <v>631</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_14</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="n">
+        <v>632</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_15</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="n">
+        <v>633</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_16</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="n">
+        <v>634</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_17</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="n">
+        <v>635</v>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_18</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="n">
+        <v>636</v>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_19</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="n">
+        <v>637</v>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_20</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="n">
+        <v>638</v>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_21</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="n">
+        <v>639</v>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_22</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="n">
+        <v>640</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>s_hour_scen2_2_4_23</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="n">
+        <v>641</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_00</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="n">
+        <v>642</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_01</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="n">
+        <v>643</v>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_02</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="n">
+        <v>644</v>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_03</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="n">
+        <v>645</v>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_04</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="n">
+        <v>646</v>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_05</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="n">
+        <v>647</v>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_06</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="n">
+        <v>648</v>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_07</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="n">
+        <v>649</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_08</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="n">
+        <v>650</v>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_09</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="n">
+        <v>651</v>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_10</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="n">
+        <v>652</v>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_11</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="n">
+        <v>653</v>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_12</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="n">
+        <v>654</v>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_13</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="n">
+        <v>655</v>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_14</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="n">
+        <v>656</v>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_15</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="n">
+        <v>657</v>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_16</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="n">
+        <v>658</v>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_17</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="n">
+        <v>659</v>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_18</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="n">
+        <v>660</v>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_19</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="n">
+        <v>661</v>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_20</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="n">
+        <v>662</v>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_21</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="n">
+        <v>663</v>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_0_22</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="n">
+        <v>664</v>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_00</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="n">
+        <v>665</v>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_01</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="n">
+        <v>666</v>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_02</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="n">
+        <v>667</v>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_03</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="n">
+        <v>668</v>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_04</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="n">
+        <v>669</v>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_05</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="n">
+        <v>670</v>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_06</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="n">
+        <v>671</v>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_07</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="n">
+        <v>672</v>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_08</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="n">
+        <v>673</v>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_09</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="n">
+        <v>674</v>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_10</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="n">
+        <v>675</v>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_11</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="n">
+        <v>676</v>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_12</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="n">
+        <v>677</v>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_13</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="n">
+        <v>678</v>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_14</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="n">
+        <v>679</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_15</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="n">
+        <v>680</v>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_16</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="n">
+        <v>681</v>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_17</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="n">
+        <v>682</v>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_18</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="n">
+        <v>683</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_19</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="n">
+        <v>684</v>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_0_1_20</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="n">
+        <v>685</v>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_00</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="n">
+        <v>686</v>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_01</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="n">
+        <v>687</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_02</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="n">
+        <v>688</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_03</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="n">
+        <v>689</v>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_04</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="n">
+        <v>690</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_05</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="n">
+        <v>691</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_06</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="n">
+        <v>692</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_07</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="n">
+        <v>693</v>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_08</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="n">
+        <v>694</v>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_09</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="n">
+        <v>695</v>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_10</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="n">
+        <v>696</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_11</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="n">
+        <v>697</v>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_12</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="n">
+        <v>698</v>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_13</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="n">
+        <v>699</v>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_14</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_15</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="n">
+        <v>701</v>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_16</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="n">
+        <v>702</v>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_17</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="n">
+        <v>703</v>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_18</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="n">
+        <v>704</v>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_2_19</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="n">
+        <v>705</v>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_00</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="n">
+        <v>706</v>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_01</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="n">
+        <v>707</v>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_02</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="n">
+        <v>708</v>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_03</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="n">
+        <v>709</v>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_04</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="n">
+        <v>710</v>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_05</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="n">
+        <v>711</v>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_06</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="n">
+        <v>712</v>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_07</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="n">
+        <v>713</v>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_08</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="n">
+        <v>714</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_09</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="n">
+        <v>715</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_10</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="1" t="n">
+        <v>716</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_11</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="1" t="n">
+        <v>717</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_12</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="1" t="n">
+        <v>718</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_13</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="1" t="n">
+        <v>719</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_14</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="1" t="n">
+        <v>720</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_15</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="1" t="n">
+        <v>721</v>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_16</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="1" t="n">
+        <v>722</v>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_17</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="1" t="n">
+        <v>723</v>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_18</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="1" t="n">
+        <v>724</v>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_19</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="1" t="n">
+        <v>725</v>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_20</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="1" t="n">
+        <v>726</v>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_3_21</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="1" t="n">
+        <v>727</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_00</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="n">
+        <v>728</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_01</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1" t="n">
+        <v>729</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_02</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="n">
+        <v>730</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_03</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="1" t="n">
+        <v>731</v>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_04</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1" t="n">
+        <v>732</v>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_05</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="n">
+        <v>733</v>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_06</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1" t="n">
+        <v>734</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_07</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="n">
+        <v>735</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_08</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="n">
+        <v>736</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_09</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="n">
+        <v>737</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_10</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="n">
+        <v>738</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_11</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="n">
+        <v>739</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_12</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="1" t="n">
+        <v>740</v>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_13</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="n">
+        <v>741</v>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_14</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="1" t="n">
+        <v>742</v>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_15</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="n">
+        <v>743</v>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_16</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="n">
+        <v>744</v>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_17</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="n">
+        <v>745</v>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_18</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="1" t="n">
+        <v>746</v>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_19</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="n">
+        <v>747</v>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_20</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="n">
+        <v>748</v>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_21</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="n">
+        <v>749</v>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_22</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="n">
+        <v>750</v>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_1_4_23</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="n">
+        <v>751</v>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_00</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="n">
+        <v>752</v>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_01</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="n">
+        <v>753</v>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_02</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="n">
+        <v>754</v>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_03</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="n">
+        <v>755</v>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_04</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="1" t="n">
+        <v>756</v>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_05</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="1" t="n">
+        <v>757</v>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_06</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="1" t="n">
+        <v>758</v>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_07</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="1" t="n">
+        <v>759</v>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_08</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="1" t="n">
+        <v>760</v>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_09</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="1" t="n">
+        <v>761</v>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_10</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="1" t="n">
+        <v>762</v>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_11</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="1" t="n">
+        <v>763</v>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_12</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="1" t="n">
+        <v>764</v>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_13</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="1" t="n">
+        <v>765</v>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_14</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="1" t="n">
+        <v>766</v>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_15</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="1" t="n">
+        <v>767</v>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_16</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="1" t="n">
+        <v>768</v>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_17</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="1" t="n">
+        <v>769</v>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_18</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="1" t="n">
+        <v>770</v>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_2_19</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="1" t="n">
+        <v>771</v>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_00</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="1" t="n">
+        <v>772</v>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_01</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="1" t="n">
+        <v>773</v>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_02</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="1" t="n">
+        <v>774</v>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_03</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="1" t="n">
+        <v>775</v>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_04</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="1" t="n">
+        <v>776</v>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_05</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="1" t="n">
+        <v>777</v>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_06</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="1" t="n">
+        <v>778</v>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_07</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="1" t="n">
+        <v>779</v>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_08</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="1" t="n">
+        <v>780</v>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_09</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="1" t="n">
+        <v>781</v>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_10</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="1" t="n">
+        <v>782</v>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_11</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="1" t="n">
+        <v>783</v>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_12</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="1" t="n">
+        <v>784</v>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_13</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="1" t="n">
+        <v>785</v>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_14</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="1" t="n">
+        <v>786</v>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_15</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="1" t="n">
+        <v>787</v>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_16</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="1" t="n">
+        <v>788</v>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_17</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="1" t="n">
+        <v>789</v>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_18</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="1" t="n">
+        <v>790</v>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_19</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="1" t="n">
+        <v>791</v>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_20</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="1" t="n">
+        <v>792</v>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_3_21</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="1" t="n">
+        <v>793</v>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_00</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="1" t="n">
+        <v>794</v>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_01</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="1" t="n">
+        <v>795</v>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_02</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="1" t="n">
+        <v>796</v>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_03</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="1" t="n">
+        <v>797</v>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_04</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="1" t="n">
+        <v>798</v>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_05</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="1" t="n">
+        <v>799</v>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_06</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="1" t="n">
+        <v>800</v>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_07</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="1" t="n">
+        <v>801</v>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_08</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="1" t="n">
+        <v>802</v>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_09</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="1" t="n">
+        <v>803</v>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_10</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>804</v>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_11</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>805</v>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_12</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>806</v>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_13</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="1" t="n">
+        <v>807</v>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_14</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="1" t="n">
+        <v>808</v>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_15</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="1" t="n">
+        <v>809</v>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_16</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="1" t="n">
+        <v>810</v>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_17</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="1" t="n">
+        <v>811</v>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_18</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="1" t="n">
+        <v>812</v>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_19</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="1" t="n">
+        <v>813</v>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_20</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="1" t="n">
+        <v>814</v>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_21</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="1" t="n">
+        <v>815</v>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_22</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="1" t="n">
+        <v>816</v>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>s_hour_scen3_2_4_23</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="1" t="n">
+        <v>817</v>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>startingtime_(0,_0)</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="1" t="n">
+        <v>818</v>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>startingtime_(0,_1)</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="1" t="n">
+        <v>819</v>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>startingtime_(0,_2)</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="1" t="n">
+        <v>820</v>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>startingtime_(0,_3)</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="1" t="n">
+        <v>821</v>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>startingtime_(0,_4)</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="1" t="n">
+        <v>822</v>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>startingtime_(1,_0)</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="1" t="n">
+        <v>823</v>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>startingtime_(1,_1)</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="1" t="n">
+        <v>824</v>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>startingtime_(1,_2)</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="1" t="n">
+        <v>825</v>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>startingtime_(1,_3)</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="1" t="n">
+        <v>826</v>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>startingtime_(1,_4)</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="1" t="n">
+        <v>827</v>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>startingtime_(2,_0)</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="1" t="n">
+        <v>828</v>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>startingtime_(2,_1)</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="1" t="n">
+        <v>829</v>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>startingtime_(2,_2)</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="1" t="n">
+        <v>830</v>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>startingtime_(2,_3)</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="1" t="n">
+        <v>831</v>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>startingtime_(2,_4)</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="1" t="n">
+        <v>832</v>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>startingtime_(3,_0)</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="1" t="n">
+        <v>833</v>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>startingtime_(3,_1)</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="1" t="n">
+        <v>834</v>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>startingtime_(3,_2)</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="1" t="n">
+        <v>835</v>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>startingtime_(3,_3)</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="1" t="n">
+        <v>836</v>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>startingtime_(3,_4)</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="1" t="n">
+        <v>837</v>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>x_(0,_0,_0)</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="1" t="n">
+        <v>838</v>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>x_(0,_0,_1)</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="1" t="n">
+        <v>839</v>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>x_(0,_1,_2)</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="1" t="n">
+        <v>840</v>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>x_(0,_1,_3)</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="1" t="n">
+        <v>841</v>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>x_(0,_1,_4)</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="1" t="n">
+        <v>842</v>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>x_(0,_2,_2)</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="1" t="n">
+        <v>843</v>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>x_(0,_2,_3)</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="1" t="n">
+        <v>844</v>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>x_(0,_2,_4)</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="1" t="n">
+        <v>845</v>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>x_(1,_0,_0)</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="1" t="n">
+        <v>846</v>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>x_(1,_0,_1)</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="1" t="n">
+        <v>847</v>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>x_(1,_1,_2)</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="1" t="n">
+        <v>848</v>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>x_(1,_1,_3)</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="1" t="n">
+        <v>849</v>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>x_(1,_1,_4)</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="1" t="n">
+        <v>850</v>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>x_(1,_2,_2)</t>
+        </is>
+      </c>
+      <c r="C852" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="1" t="n">
+        <v>851</v>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>x_(1,_2,_3)</t>
+        </is>
+      </c>
+      <c r="C853" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="1" t="n">
+        <v>852</v>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>x_(1,_2,_4)</t>
+        </is>
+      </c>
+      <c r="C854" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="1" t="n">
+        <v>853</v>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>x_(2,_0,_0)</t>
+        </is>
+      </c>
+      <c r="C855" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="1" t="n">
+        <v>854</v>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>x_(2,_0,_1)</t>
+        </is>
+      </c>
+      <c r="C856" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="1" t="n">
+        <v>855</v>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>x_(2,_1,_2)</t>
+        </is>
+      </c>
+      <c r="C857" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="1" t="n">
+        <v>856</v>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>x_(2,_1,_3)</t>
+        </is>
+      </c>
+      <c r="C858" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="1" t="n">
+        <v>857</v>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>x_(2,_1,_4)</t>
+        </is>
+      </c>
+      <c r="C859" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="1" t="n">
+        <v>858</v>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>x_(2,_2,_2)</t>
+        </is>
+      </c>
+      <c r="C860" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="1" t="n">
+        <v>859</v>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>x_(2,_2,_3)</t>
+        </is>
+      </c>
+      <c r="C861" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="1" t="n">
+        <v>860</v>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
           <t>x_(2,_2,_4)</t>
         </is>
       </c>
-      <c r="C572" t="n">
+      <c r="C862" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="1" t="n">
+        <v>861</v>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>x_(3,_0,_0)</t>
+        </is>
+      </c>
+      <c r="C863" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="1" t="n">
+        <v>862</v>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>x_(3,_0,_1)</t>
+        </is>
+      </c>
+      <c r="C864" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="1" t="n">
+        <v>863</v>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>x_(3,_1,_2)</t>
+        </is>
+      </c>
+      <c r="C865" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="1" t="n">
+        <v>864</v>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>x_(3,_1,_3)</t>
+        </is>
+      </c>
+      <c r="C866" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="1" t="n">
+        <v>865</v>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>x_(3,_1,_4)</t>
+        </is>
+      </c>
+      <c r="C867" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="1" t="n">
+        <v>866</v>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>x_(3,_2,_2)</t>
+        </is>
+      </c>
+      <c r="C868" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="1" t="n">
+        <v>867</v>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>x_(3,_2,_3)</t>
+        </is>
+      </c>
+      <c r="C869" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="1" t="n">
+        <v>868</v>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>x_(3,_2,_4)</t>
+        </is>
+      </c>
+      <c r="C870" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
